--- a/public/templates/student_import_template.xlsx
+++ b/public/templates/student_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FPT SHOP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64489B0A-E90E-4484-A4F4-B454CDCFC123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC8A28-B2DA-4DB5-AF7F-4588261E8A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t>GIÁO XỨ .............................................</t>
   </si>
@@ -213,6 +213,24 @@
   </si>
   <si>
     <t>15/10/2017</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>ghi_chu</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>so_dien_thoai</t>
   </si>
 </sst>
 </file>
@@ -406,6 +424,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -419,25 +456,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,55 +759,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15" style="13" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" style="13" customWidth="1"/>
+    <col min="10" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-    </row>
-    <row r="3" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,7 +828,7 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -814,8 +843,17 @@
       <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -825,7 +863,7 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -840,8 +878,17 @@
       <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
@@ -851,7 +898,7 @@
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="14" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -860,14 +907,17 @@
       <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="14"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -877,7 +927,7 @@
       <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>56</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -886,14 +936,17 @@
       <c r="F7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="17" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="15"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
@@ -903,7 +956,7 @@
       <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -912,31 +965,37 @@
       <c r="F8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="16" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="I8" s="14"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/student_import_template.xlsx
+++ b/public/templates/student_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FPT SHOP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC8A28-B2DA-4DB5-AF7F-4588261E8A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C9739-29F3-48F0-B062-7DA8E93DD754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>GIÁO XỨ .............................................</t>
   </si>
@@ -80,48 +80,6 @@
     <t>ho_ten_me</t>
   </si>
   <si>
-    <t>Giuse</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn</t>
-  </si>
-  <si>
-    <t>An</t>
-  </si>
-  <si>
-    <t>Nam</t>
-  </si>
-  <si>
-    <t>Giáo họ Chính</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>Trần Thị</t>
-  </si>
-  <si>
-    <t>Bình</t>
-  </si>
-  <si>
-    <t>Nữ</t>
-  </si>
-  <si>
-    <t>Giáo họ Thánh Tâm</t>
-  </si>
-  <si>
-    <t>Phêrô</t>
-  </si>
-  <si>
-    <t>Lê Văn</t>
-  </si>
-  <si>
-    <t>Cường</t>
-  </si>
-  <si>
-    <t>Giáo họ Mân Côi</t>
-  </si>
-  <si>
     <t>(*) Nhập dữ liệu từ dòng 6. Không xóa dòng 4 và 5. ten_thanh và giao_ho phải khớp tên trong hệ thống.</t>
   </si>
   <si>
@@ -186,33 +144,6 @@
   </si>
   <si>
     <t>Họ tên mẹ. Không bắt buộc.</t>
-  </si>
-  <si>
-    <t>01/07/2017</t>
-  </si>
-  <si>
-    <t>02/05/2017</t>
-  </si>
-  <si>
-    <t>Giuse Nguyễn Văn Bình</t>
-  </si>
-  <si>
-    <t>Giuse Trần Văn Hùng</t>
-  </si>
-  <si>
-    <t>Giuse Lê Văn Dũng</t>
-  </si>
-  <si>
-    <t>Maria Trần Thị Lan</t>
-  </si>
-  <si>
-    <t>Maria Lê Thị Hoa</t>
-  </si>
-  <si>
-    <t>Maria Nguyễn Thị Mai</t>
-  </si>
-  <si>
-    <t>15/10/2017</t>
   </si>
   <si>
     <t>Số điện thoại</t>
@@ -237,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,13 +243,8 @@
       <sz val="9"/>
       <name val="Courier New"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,12 +267,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEBF3FB"/>
         <bgColor rgb="FFEBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F8FD"/>
-        <bgColor rgb="FFF2F8FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -392,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,12 +320,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -431,18 +345,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -759,64 +661,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="15" style="13" customWidth="1"/>
+    <col min="4" max="4" width="15" style="11" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="24" style="13" customWidth="1"/>
+    <col min="9" max="9" width="24" style="11" customWidth="1"/>
     <col min="10" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -828,7 +730,7 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -843,14 +745,14 @@
       <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>64</v>
+      <c r="I4" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -863,7 +765,7 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -878,121 +780,34 @@
       <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>69</v>
+      <c r="I5" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A21:K21"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -1012,128 +827,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+    <row r="13" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+    <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="15" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+    <row r="16" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+    </row>
+    <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+    <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/student_import_template.xlsx
+++ b/public/templates/student_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FPT SHOP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C9739-29F3-48F0-B062-7DA8E93DD754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AA5B1F-8530-4FAF-B5BA-54A47D0C2D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,159 +16,212 @@
     <sheet name="Danh sách học sinh" sheetId="1" r:id="rId1"/>
     <sheet name="Hướng dẫn" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
-  <si>
-    <t>GIÁO XỨ .............................................</t>
-  </si>
-  <si>
-    <t>Năm học: ................</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+  <si>
+    <t>Tên thánh</t>
+  </si>
+  <si>
+    <t>Họ &amp; tên đệm</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>Ngày sinh</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Giáo họ</t>
+  </si>
+  <si>
+    <t>Họ tên bố</t>
+  </si>
+  <si>
+    <t>Họ tên mẹ</t>
+  </si>
+  <si>
+    <t>ten_thanh</t>
+  </si>
+  <si>
+    <t>ho_ten_dem</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>ngay_sinh</t>
+  </si>
+  <si>
+    <t>gioi_tinh</t>
+  </si>
+  <si>
+    <t>giao_ho</t>
+  </si>
+  <si>
+    <t>ho_ten_bo</t>
+  </si>
+  <si>
+    <t>ho_ten_me</t>
+  </si>
+  <si>
+    <t>HƯỚNG DẪN NHẬP LIỆU</t>
+  </si>
+  <si>
+    <t>1. CẤU TRÚC FILE</t>
+  </si>
+  <si>
+    <t>Dòng 1–2</t>
+  </si>
+  <si>
+    <t>Dòng 3</t>
+  </si>
+  <si>
+    <t>Tiêu đề bảng — không chỉnh sửa</t>
+  </si>
+  <si>
+    <t>Dòng 4</t>
+  </si>
+  <si>
+    <t>Tên cột tiếng Việt — không chỉnh sửa</t>
+  </si>
+  <si>
+    <t>Dòng 5</t>
+  </si>
+  <si>
+    <t>Tên cột kỹ thuật — KHÔNG xóa, KHÔNG đổi</t>
+  </si>
+  <si>
+    <t>Dòng 6+</t>
+  </si>
+  <si>
+    <t>Nhập dữ liệu học sinh từ đây</t>
+  </si>
+  <si>
+    <t>2. CHI TIẾT TỪNG CỘT</t>
+  </si>
+  <si>
+    <t>Phải khớp tên thánh trong hệ thống. Sai → bỏ trống.</t>
+  </si>
+  <si>
+    <t>Họ và tên đệm. VD: Nguyễn Văn  ← BẮT BUỘC</t>
+  </si>
+  <si>
+    <t>Tên. VD: An  ← BẮT BUỘC</t>
+  </si>
+  <si>
+    <t>Nhập: Nam hoặc Nữ (hoặc male/female)  ← BẮT BUỘC</t>
+  </si>
+  <si>
+    <t>Phải khớp tên giáo họ trong hệ thống. Sai → bỏ trống.</t>
+  </si>
+  <si>
+    <t>Họ tên bố. Không bắt buộc.</t>
+  </si>
+  <si>
+    <t>Họ tên mẹ. Không bắt buộc.</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>ghi_chu</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>so_dien_thoai</t>
+  </si>
+  <si>
+    <t>Mã học sinh</t>
+  </si>
+  <si>
+    <t>ma_hoc_sinh</t>
+  </si>
+  <si>
+    <t>Thông tin giáo xứ (không bắt buộc) — điền vào ô chấm (...)</t>
+  </si>
+  <si>
+    <r>
+      <t>(*) Nhập dữ liệu từ dòng 6. Không xóa dòng 4 và 5. ten_thanh và giao_ho phải khớp tên trong hệ thống. Hãy đọc hướng dẫn kỹ hơn ở Sheet</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hướng dẫn</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NHỚ XÓA DÒNG NÀY NHA!!!</t>
+    </r>
+  </si>
+  <si>
+    <t>Định dạng: dd/mm/yyyy   ← BẮT BUỘC</t>
+  </si>
+  <si>
+    <t>Đúng định dạng (10 chữ số)</t>
+  </si>
+  <si>
+    <t>Đúng định dạng email.</t>
+  </si>
+  <si>
+    <t>Chỉ nhập mã nếu cập nhật học sinh. Để trống nếu thêm mới.</t>
+  </si>
+  <si>
+    <t>Năm học: ..................</t>
+  </si>
+  <si>
+    <t>GIÁO XỨ ................................</t>
   </si>
   <si>
     <t>DANH SÁCH GHI DANH HỌC SINH</t>
-  </si>
-  <si>
-    <t>Tên thánh</t>
-  </si>
-  <si>
-    <t>Họ &amp; tên đệm</t>
-  </si>
-  <si>
-    <t>Tên</t>
-  </si>
-  <si>
-    <t>Ngày sinh</t>
-  </si>
-  <si>
-    <t>Giới tính</t>
-  </si>
-  <si>
-    <t>Giáo họ</t>
-  </si>
-  <si>
-    <t>Họ tên bố</t>
-  </si>
-  <si>
-    <t>Họ tên mẹ</t>
-  </si>
-  <si>
-    <t>ten_thanh</t>
-  </si>
-  <si>
-    <t>ho_ten_dem</t>
-  </si>
-  <si>
-    <t>ten</t>
-  </si>
-  <si>
-    <t>ngay_sinh</t>
-  </si>
-  <si>
-    <t>gioi_tinh</t>
-  </si>
-  <si>
-    <t>giao_ho</t>
-  </si>
-  <si>
-    <t>ho_ten_bo</t>
-  </si>
-  <si>
-    <t>ho_ten_me</t>
-  </si>
-  <si>
-    <t>(*) Nhập dữ liệu từ dòng 6. Không xóa dòng 4 và 5. ten_thanh và giao_ho phải khớp tên trong hệ thống.</t>
-  </si>
-  <si>
-    <t>HƯỚNG DẪN NHẬP LIỆU</t>
-  </si>
-  <si>
-    <t>1. CẤU TRÚC FILE</t>
-  </si>
-  <si>
-    <t>Dòng 1–2</t>
-  </si>
-  <si>
-    <t>Thông tin giáo xứ — điền vào ô chấm (...)</t>
-  </si>
-  <si>
-    <t>Dòng 3</t>
-  </si>
-  <si>
-    <t>Tiêu đề bảng — không chỉnh sửa</t>
-  </si>
-  <si>
-    <t>Dòng 4</t>
-  </si>
-  <si>
-    <t>Tên cột tiếng Việt — không chỉnh sửa</t>
-  </si>
-  <si>
-    <t>Dòng 5</t>
-  </si>
-  <si>
-    <t>Tên cột kỹ thuật — KHÔNG xóa, KHÔNG đổi</t>
-  </si>
-  <si>
-    <t>Dòng 6+</t>
-  </si>
-  <si>
-    <t>Nhập dữ liệu học sinh từ đây</t>
-  </si>
-  <si>
-    <t>2. CHI TIẾT TỪNG CỘT</t>
-  </si>
-  <si>
-    <t>Phải khớp tên thánh trong hệ thống. Sai → bỏ trống.</t>
-  </si>
-  <si>
-    <t>Họ và tên đệm. VD: Nguyễn Văn  ← BẮT BUỘC</t>
-  </si>
-  <si>
-    <t>Tên. VD: An  ← BẮT BUỘC</t>
-  </si>
-  <si>
-    <t>Định dạng: dd/mm/yyyy hoặc yyyy-mm-dd  ← BẮT BUỘC</t>
-  </si>
-  <si>
-    <t>Nhập: Nam hoặc Nữ (hoặc male/female)  ← BẮT BUỘC</t>
-  </si>
-  <si>
-    <t>Phải khớp tên giáo họ trong hệ thống. Sai → bỏ trống.</t>
-  </si>
-  <si>
-    <t>Họ tên bố. Không bắt buộc.</t>
-  </si>
-  <si>
-    <t>Họ tên mẹ. Không bắt buộc.</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>ghi_chu</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>so_dien_thoai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0000000000"/>
+  </numFmts>
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,23 +234,27 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1E3A5F"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -205,43 +262,80 @@
       <sz val="8"/>
       <color rgb="FF555555"/>
       <name val="Courier New"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF888888"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF1E3A5F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1E3A5F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -270,7 +364,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -288,8 +382,17 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF1E3A5F"/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -297,6 +400,28 @@
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFCCCCCC"/>
       </right>
@@ -312,16 +437,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -335,28 +457,54 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,156 +809,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="15" style="11" customWidth="1"/>
+    <col min="4" max="4" width="15" style="9" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="24" style="11" customWidth="1"/>
-    <col min="10" max="11" width="24" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+    </row>
+    <row r="3" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="1:11" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="I4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
+    </row>
+    <row r="16" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A16:L16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -818,140 +978,171 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:C18"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="3" max="3" width="73" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14"/>
+    </row>
+    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="9" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="19" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="C10" s="19"/>
+    </row>
+    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+    <row r="13" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+    <row r="16" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="4" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>40</v>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B10:C10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/templates/student_import_template.xlsx
+++ b/public/templates/student_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\WORKING\lavarel_qlgx\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7152F730-370D-4FFD-924A-3D0360245C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF96A41-1FD8-4169-8AA1-FAD759C1E5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Tên thánh</t>
   </si>
@@ -178,50 +178,12 @@
   <si>
     <t>DANH SÁCH GHI DANH HỌC SINH</t>
   </si>
-  <si>
-    <r>
-      <t>(*) Nhập dữ liệu từ dòng 6. Không xóa dòng 4 và 5. ten_thanh và giao_ho phải khớp tên trong hệ thống. Hãy đọc hướng dẫn kỹ hơn ở Sheet</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Hướng dẫn</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>NHỚ XÓA DÒNG NÀY NHA!!!</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,37 +228,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF888888"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -445,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -457,10 +388,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -492,32 +423,24 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -828,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:L999"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="7" customWidth="1"/>
@@ -1109,21 +1032,19 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
@@ -14887,30 +14808,15 @@
       <c r="K999" s="8"/>
       <c r="L999" s="8"/>
     </row>
-    <row r="1000" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1000" s="8"/>
-      <c r="B1000" s="8"/>
-      <c r="C1000" s="8"/>
-      <c r="D1000" s="9"/>
-      <c r="E1000" s="8"/>
-      <c r="F1000" s="8"/>
-      <c r="G1000" s="8"/>
-      <c r="H1000" s="8"/>
-      <c r="I1000" s="9"/>
-      <c r="J1000" s="8"/>
-      <c r="K1000" s="8"/>
-      <c r="L1000" s="8"/>
-    </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="4">
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A16:L16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E15 E17:E1000" xr:uid="{45C970E0-4C01-4AFA-8896-60FCC444E033}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E15 E16:E999" xr:uid="{45C970E0-4C01-4AFA-8896-60FCC444E033}">
       <formula1>"Nam, Nữ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14931,10 +14837,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="24"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2"/>
@@ -14989,10 +14895,10 @@
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">

--- a/public/templates/student_import_template.xlsx
+++ b/public/templates/student_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\WORKING\lavarel_qlgx\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF96A41-1FD8-4169-8AA1-FAD759C1E5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DD1FCE-D98D-4006-AC52-F68431FE2AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14809,7 +14809,7 @@
       <c r="L999" s="8"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
